--- a/ExperimentSummarySheet_Ex1.xlsx
+++ b/ExperimentSummarySheet_Ex1.xlsx
@@ -8,7 +8,7 @@
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="35">
   <si>
     <t xml:space="preserve">Group Name/Student Name</t>
   </si>
@@ -53,6 +53,78 @@
   </si>
   <si>
     <t xml:space="preserve">Other</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Group_22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Naive Bayes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BoW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">As task 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BASELINE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tfidf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Model is extremly unsure and classifies almost everything as neutral, we observe a recall of 0.98 for “neutral” and a precision of 1.0 for “negative” with a recall of 0.06 for “negative”</t>
+  </si>
+  <si>
+    <t xml:space="preserve">As task 2, without additional stop words</t>
+  </si>
+  <si>
+    <t xml:space="preserve">super minor performance gain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no difference in performance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">As task 2, no number replacement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">super minor performance loss</t>
+  </si>
+  <si>
+    <t xml:space="preserve">As task 2, no lemmatization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">minor increase in performance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oversampling</t>
+  </si>
+  <si>
+    <t xml:space="preserve">After oversampling the model gets more confident in labling “negative”, however while the recall increases from 0.5 → 0.75 (class negative),  the precision decreases from 0.61→0.4 (class negative), meaning it also makes more misstakes. At the same time recall for class “neutral” decreases 0.86 → 0.71, the model recognises the largest class not as good as before. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">model starts getting usable, as the “negative” class is finally recognized. While the model starts labeling smaller classes more often, its precision decreases. The gain in recall leads to a higher f1 score though. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Undersampling</t>
+  </si>
+  <si>
+    <t xml:space="preserve">again the model gets more confidence for the smallest class, at the cost of performance of the bigger classes. Also the precision for the smalles class decreases meaning, while it gets confidence, it also tends to misjudge.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">as task 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">done via ComplementNB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">slightly better f1, hardly noteworthy, when looking at precision/recall for the classes, we seem to gain a bit more balance though, so overall I would claim this model to be the strongest so far</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Huge recall improvement across the board. The shyness to label class 2 (negative) is basically gone. </t>
   </si>
 </sst>
 </file>
@@ -136,12 +208,20 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -157,57 +237,617 @@
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office">
+  <a:themeElements>
+    <a:clrScheme name="LibreOffice">
+      <a:dk1>
+        <a:srgbClr val="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:srgbClr val="ffffff"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="000000"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="ffffff"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="18a303"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="0369a3"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="a33e03"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="8e03a3"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="c99c00"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="c9211e"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0000ee"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="551a8b"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme>
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:K1"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:K15"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="25.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="14.28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="14.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="16.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="9.7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="9.15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="16.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="11.51"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="3.06"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="11.68"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="20.95"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="14.25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="16.09"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="17.68"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="9.7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="9.15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="17.56"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="11" style="2" width="8.54"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="3" t="s">
         <v>10</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H2" s="1" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="I2" s="1" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H3" s="1" t="n">
+        <v>0.69</v>
+      </c>
+      <c r="I3" s="1" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H4" s="1" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="I4" s="1" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H5" s="1" t="n">
+        <v>0.69</v>
+      </c>
+      <c r="I5" s="1" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H6" s="1" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="I6" s="1" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H7" s="1" t="n">
+        <v>0.69</v>
+      </c>
+      <c r="I7" s="1" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H8" s="1" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="I8" s="1" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H9" s="1" t="n">
+        <v>0.69</v>
+      </c>
+      <c r="I9" s="1" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H10" s="1" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="I10" s="1" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="J10" s="0"/>
+      <c r="K10" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H11" s="1" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="I11" s="1" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="J11" s="0"/>
+      <c r="K11" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H12" s="1" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="I12" s="1" t="n">
+        <v>0.53</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H13" s="1" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="I13" s="1" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="J13" s="0"/>
+      <c r="K13" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H14" s="1" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="I14" s="1" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="K14" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H15" s="1" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="I15" s="1" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="K15" s="2" t="s">
+        <v>34</v>
       </c>
     </row>
   </sheetData>

--- a/ExperimentSummarySheet_Ex1.xlsx
+++ b/ExperimentSummarySheet_Ex1.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="37">
   <si>
     <t xml:space="preserve">Group Name/Student Name</t>
   </si>
@@ -76,7 +76,7 @@
     <t xml:space="preserve">Tfidf</t>
   </si>
   <si>
-    <t xml:space="preserve">Model is extremly unsure and classifies almost everything as neutral, we observe a recall of 0.98 for “neutral” and a precision of 1.0 for “negative” with a recall of 0.06 for “negative”</t>
+    <t xml:space="preserve">BASELINE, Model is extremly unsure and classifies almost everything as neutral, we observe a recall of 0.98 for “neutral” and a precision of 1.0 for “negative” with a recall of 0.06 for “negative”</t>
   </si>
   <si>
     <t xml:space="preserve">As task 2, without additional stop words</t>
@@ -125,6 +125,12 @@
   </si>
   <si>
     <t xml:space="preserve">Huge recall improvement across the board. The shyness to label class 2 (negative) is basically gone. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Naive Bayes Binary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Significant improvement to baseline, this was expected tho, as the task got easier</t>
   </si>
 </sst>
 </file>
@@ -208,16 +214,12 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -348,12 +350,12 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:K15"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="11.51"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="3.06"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="11.68"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="3.06"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="17.68"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="20.95"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="14.25"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="16.09"/>
@@ -361,41 +363,41 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="9.7"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="9.15"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="17.56"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="11" style="2" width="8.54"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="11" style="1" width="8.54"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="3" t="s">
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
     </row>
@@ -403,10 +405,10 @@
       <c r="A2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="C2" s="2" t="s">
+      <c r="B2" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D2" s="1" t="s">
@@ -427,7 +429,7 @@
       <c r="I2" s="1" t="n">
         <v>0.65</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="K2" s="1" t="s">
         <v>16</v>
       </c>
     </row>
@@ -435,10 +437,10 @@
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="C3" s="2" t="s">
+      <c r="B3" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D3" s="1" t="s">
@@ -459,21 +461,18 @@
       <c r="I3" s="1" t="n">
         <v>0.46</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="K3" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="C4" s="2" t="s">
+      <c r="B4" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D4" s="1" t="s">
@@ -494,7 +493,7 @@
       <c r="I4" s="1" t="n">
         <v>0.66</v>
       </c>
-      <c r="K4" s="2" t="s">
+      <c r="K4" s="1" t="s">
         <v>20</v>
       </c>
     </row>
@@ -502,10 +501,10 @@
       <c r="A5" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="C5" s="2" t="s">
+      <c r="B5" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D5" s="1" t="s">
@@ -526,7 +525,7 @@
       <c r="I5" s="1" t="n">
         <v>0.46</v>
       </c>
-      <c r="K5" s="2" t="s">
+      <c r="K5" s="1" t="s">
         <v>21</v>
       </c>
     </row>
@@ -534,10 +533,10 @@
       <c r="A6" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="C6" s="2" t="s">
+      <c r="B6" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D6" s="1" t="s">
@@ -558,7 +557,7 @@
       <c r="I6" s="1" t="n">
         <v>0.64</v>
       </c>
-      <c r="K6" s="2" t="s">
+      <c r="K6" s="1" t="s">
         <v>23</v>
       </c>
     </row>
@@ -566,10 +565,10 @@
       <c r="A7" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="C7" s="2" t="s">
+      <c r="B7" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D7" s="1" t="s">
@@ -590,7 +589,7 @@
       <c r="I7" s="1" t="n">
         <v>0.46</v>
       </c>
-      <c r="K7" s="2" t="s">
+      <c r="K7" s="1" t="s">
         <v>21</v>
       </c>
     </row>
@@ -598,10 +597,10 @@
       <c r="A8" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="C8" s="2" t="s">
+      <c r="B8" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D8" s="1" t="s">
@@ -622,7 +621,7 @@
       <c r="I8" s="1" t="n">
         <v>0.66</v>
       </c>
-      <c r="K8" s="2" t="s">
+      <c r="K8" s="1" t="s">
         <v>25</v>
       </c>
     </row>
@@ -630,10 +629,10 @@
       <c r="A9" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="C9" s="2" t="s">
+      <c r="B9" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="C9" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D9" s="1" t="s">
@@ -654,7 +653,7 @@
       <c r="I9" s="1" t="n">
         <v>0.47</v>
       </c>
-      <c r="K9" s="2" t="s">
+      <c r="K9" s="1" t="s">
         <v>25</v>
       </c>
     </row>
@@ -662,10 +661,10 @@
       <c r="A10" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B10" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="C10" s="2" t="s">
+      <c r="B10" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="C10" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D10" s="1" t="s">
@@ -686,7 +685,6 @@
       <c r="I10" s="1" t="n">
         <v>0.59</v>
       </c>
-      <c r="J10" s="0"/>
       <c r="K10" s="1" t="s">
         <v>27</v>
       </c>
@@ -695,10 +693,10 @@
       <c r="A11" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B11" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="C11" s="2" t="s">
+      <c r="B11" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="C11" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D11" s="1" t="s">
@@ -719,7 +717,6 @@
       <c r="I11" s="1" t="n">
         <v>0.61</v>
       </c>
-      <c r="J11" s="0"/>
       <c r="K11" s="1" t="s">
         <v>28</v>
       </c>
@@ -728,10 +725,10 @@
       <c r="A12" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="C12" s="2" t="s">
+      <c r="B12" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="C12" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D12" s="1" t="s">
@@ -757,10 +754,10 @@
       <c r="A13" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B13" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="C13" s="2" t="s">
+      <c r="B13" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="C13" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D13" s="1" t="s">
@@ -781,7 +778,6 @@
       <c r="I13" s="1" t="n">
         <v>0.54</v>
       </c>
-      <c r="J13" s="0"/>
       <c r="K13" s="1" t="s">
         <v>30</v>
       </c>
@@ -790,10 +786,10 @@
       <c r="A14" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B14" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="C14" s="2" t="s">
+      <c r="B14" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="C14" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D14" s="1" t="s">
@@ -814,7 +810,7 @@
       <c r="I14" s="1" t="n">
         <v>0.67</v>
       </c>
-      <c r="K14" s="2" t="s">
+      <c r="K14" s="1" t="s">
         <v>33</v>
       </c>
     </row>
@@ -822,10 +818,10 @@
       <c r="A15" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B15" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="C15" s="2" t="s">
+      <c r="B15" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="C15" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D15" s="1" t="s">
@@ -846,8 +842,40 @@
       <c r="I15" s="1" t="n">
         <v>0.68</v>
       </c>
-      <c r="K15" s="2" t="s">
+      <c r="K15" s="1" t="s">
         <v>34</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B16" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H16" s="1" t="n">
+        <v>0.81</v>
+      </c>
+      <c r="I16" s="1" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>

--- a/ExperimentSummarySheet_Ex1.xlsx
+++ b/ExperimentSummarySheet_Ex1.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="49">
   <si>
     <t xml:space="preserve">Group Name/Student Name</t>
   </si>
@@ -131,6 +131,42 @@
   </si>
   <si>
     <t xml:space="preserve">Significant improvement to baseline, this was expected tho, as the task got easier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Feed-Forward NN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Epochs=5, hidden-dim=32, hidden-layers=1, dropout=0.3, lr=0.001, weight-decay=1e-4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Epochs=8, hidden-dim=32, hidden-layers=1, dropout=0.3, lr=0.001, weight-decay=1e-4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BASELINE, bow and tfidf perform basically exactly the same, even across precision and recall across classes, only difference is that tfidf takes 3 epochs longer to converge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no meaningful difference to baseline</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Epochs=5, hidden-dim=32, hidden-layers=1, dropout=0.3, lr=0.0005, weight-decay=1e-4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">recall gets more evenly distributed between classes, precision suffers a bit for the smaller classes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Epochs=7, hidden-dim=32, hidden-layers=1, dropout=0.3, lr=0.001, weight-decay=1e-4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">takes more epochs, recall distribution equals out very nicely, however precision suffers a lot, the model just has not enough training examples</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Epochs=16, hidden-dim=32, hidden-layers=1, dropout=0.3, lr=0.001, weight-decay=1e-4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Feed-Forward NN Binary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">As expected best performance on positive and negative class</t>
   </si>
 </sst>
 </file>
@@ -350,12 +386,12 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:K30"/>
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="11.51"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="3.06"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="17.68"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="21.81"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="20.95"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="14.25"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="16.09"/>
@@ -429,6 +465,7 @@
       <c r="I2" s="1" t="n">
         <v>0.65</v>
       </c>
+      <c r="J2" s="0"/>
       <c r="K2" s="1" t="s">
         <v>16</v>
       </c>
@@ -461,6 +498,7 @@
       <c r="I3" s="1" t="n">
         <v>0.46</v>
       </c>
+      <c r="J3" s="0"/>
       <c r="K3" s="1" t="s">
         <v>18</v>
       </c>
@@ -493,6 +531,7 @@
       <c r="I4" s="1" t="n">
         <v>0.66</v>
       </c>
+      <c r="J4" s="0"/>
       <c r="K4" s="1" t="s">
         <v>20</v>
       </c>
@@ -525,6 +564,7 @@
       <c r="I5" s="1" t="n">
         <v>0.46</v>
       </c>
+      <c r="J5" s="0"/>
       <c r="K5" s="1" t="s">
         <v>21</v>
       </c>
@@ -557,6 +597,7 @@
       <c r="I6" s="1" t="n">
         <v>0.64</v>
       </c>
+      <c r="J6" s="0"/>
       <c r="K6" s="1" t="s">
         <v>23</v>
       </c>
@@ -589,6 +630,7 @@
       <c r="I7" s="1" t="n">
         <v>0.46</v>
       </c>
+      <c r="J7" s="0"/>
       <c r="K7" s="1" t="s">
         <v>21</v>
       </c>
@@ -621,6 +663,7 @@
       <c r="I8" s="1" t="n">
         <v>0.66</v>
       </c>
+      <c r="J8" s="0"/>
       <c r="K8" s="1" t="s">
         <v>25</v>
       </c>
@@ -653,6 +696,7 @@
       <c r="I9" s="1" t="n">
         <v>0.47</v>
       </c>
+      <c r="J9" s="0"/>
       <c r="K9" s="1" t="s">
         <v>25</v>
       </c>
@@ -685,6 +729,7 @@
       <c r="I10" s="1" t="n">
         <v>0.59</v>
       </c>
+      <c r="J10" s="0"/>
       <c r="K10" s="1" t="s">
         <v>27</v>
       </c>
@@ -717,6 +762,7 @@
       <c r="I11" s="1" t="n">
         <v>0.61</v>
       </c>
+      <c r="J11" s="0"/>
       <c r="K11" s="1" t="s">
         <v>28</v>
       </c>
@@ -749,6 +795,7 @@
       <c r="I12" s="1" t="n">
         <v>0.53</v>
       </c>
+      <c r="J12" s="0"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
@@ -778,6 +825,7 @@
       <c r="I13" s="1" t="n">
         <v>0.54</v>
       </c>
+      <c r="J13" s="0"/>
       <c r="K13" s="1" t="s">
         <v>30</v>
       </c>
@@ -810,6 +858,7 @@
       <c r="I14" s="1" t="n">
         <v>0.67</v>
       </c>
+      <c r="J14" s="0"/>
       <c r="K14" s="1" t="s">
         <v>33</v>
       </c>
@@ -842,6 +891,7 @@
       <c r="I15" s="1" t="n">
         <v>0.68</v>
       </c>
+      <c r="J15" s="0"/>
       <c r="K15" s="1" t="s">
         <v>34</v>
       </c>
@@ -874,8 +924,441 @@
       <c r="I16" s="1" t="n">
         <v>0.78</v>
       </c>
+      <c r="J16" s="0"/>
       <c r="K16" s="1" t="s">
         <v>36</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J17" s="0"/>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B18" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="H18" s="1" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="I18" s="1" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J18" s="0"/>
+      <c r="K18" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B19" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="H19" s="1" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="I19" s="1" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J19" s="0"/>
+      <c r="K19" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B20" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="H20" s="1" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="I20" s="1" t="n">
+        <v>0.69</v>
+      </c>
+      <c r="J20" s="0"/>
+      <c r="K20" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B21" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="H21" s="1" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="I21" s="1" t="n">
+        <v>0.69</v>
+      </c>
+      <c r="J21" s="0"/>
+      <c r="K21" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B22" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="H22" s="1" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I22" s="1" t="n">
+        <v>0.69</v>
+      </c>
+      <c r="J22" s="0"/>
+      <c r="K22" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B23" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="H23" s="1" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I23" s="1" t="n">
+        <v>0.69</v>
+      </c>
+      <c r="J23" s="0"/>
+      <c r="K23" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B24" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="H24" s="1" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="I24" s="1" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="J24" s="0"/>
+      <c r="K24" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B25" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="H25" s="1" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="I25" s="1" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J25" s="0"/>
+      <c r="K25" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B26" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H26" s="1" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="I26" s="1" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="J26" s="0"/>
+      <c r="K26" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B27" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="H27" s="1" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="I27" s="1" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="J27" s="0"/>
+      <c r="K27" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B28" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="H28" s="1" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="I28" s="1" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="J28" s="0"/>
+      <c r="K28" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B29" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="H29" s="1" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="I29" s="1" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="J29" s="0"/>
+      <c r="K29" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B30" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="H30" s="1" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="I30" s="1" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="J30" s="0"/>
+      <c r="K30" s="1" t="s">
+        <v>48</v>
       </c>
     </row>
   </sheetData>

--- a/ExperimentSummarySheet_Ex1.xlsx
+++ b/ExperimentSummarySheet_Ex1.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="55">
   <si>
     <t xml:space="preserve">Group Name/Student Name</t>
   </si>
@@ -167,14 +167,33 @@
   </si>
   <si>
     <t xml:space="preserve">As expected best performance on positive and negative class</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FinBERT Multiclass</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FinBERT Autotokenizer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">None</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lr=2e-5, weight_decay=0.001, batch_size = 16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FinBERT Binary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Neutral removed</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="General"/>
+    <numFmt numFmtId="165" formatCode="0.00%"/>
   </numFmts>
   <fonts count="5">
     <font>
@@ -250,7 +269,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -260,6 +279,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -386,7 +409,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:K30"/>
+  <dimension ref="A1:K33"/>
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="11.51"/>
@@ -465,7 +488,6 @@
       <c r="I2" s="1" t="n">
         <v>0.65</v>
       </c>
-      <c r="J2" s="0"/>
       <c r="K2" s="1" t="s">
         <v>16</v>
       </c>
@@ -498,7 +520,6 @@
       <c r="I3" s="1" t="n">
         <v>0.46</v>
       </c>
-      <c r="J3" s="0"/>
       <c r="K3" s="1" t="s">
         <v>18</v>
       </c>
@@ -531,7 +552,6 @@
       <c r="I4" s="1" t="n">
         <v>0.66</v>
       </c>
-      <c r="J4" s="0"/>
       <c r="K4" s="1" t="s">
         <v>20</v>
       </c>
@@ -564,7 +584,6 @@
       <c r="I5" s="1" t="n">
         <v>0.46</v>
       </c>
-      <c r="J5" s="0"/>
       <c r="K5" s="1" t="s">
         <v>21</v>
       </c>
@@ -597,7 +616,6 @@
       <c r="I6" s="1" t="n">
         <v>0.64</v>
       </c>
-      <c r="J6" s="0"/>
       <c r="K6" s="1" t="s">
         <v>23</v>
       </c>
@@ -630,7 +648,6 @@
       <c r="I7" s="1" t="n">
         <v>0.46</v>
       </c>
-      <c r="J7" s="0"/>
       <c r="K7" s="1" t="s">
         <v>21</v>
       </c>
@@ -663,7 +680,6 @@
       <c r="I8" s="1" t="n">
         <v>0.66</v>
       </c>
-      <c r="J8" s="0"/>
       <c r="K8" s="1" t="s">
         <v>25</v>
       </c>
@@ -696,7 +712,6 @@
       <c r="I9" s="1" t="n">
         <v>0.47</v>
       </c>
-      <c r="J9" s="0"/>
       <c r="K9" s="1" t="s">
         <v>25</v>
       </c>
@@ -729,7 +744,6 @@
       <c r="I10" s="1" t="n">
         <v>0.59</v>
       </c>
-      <c r="J10" s="0"/>
       <c r="K10" s="1" t="s">
         <v>27</v>
       </c>
@@ -762,7 +776,6 @@
       <c r="I11" s="1" t="n">
         <v>0.61</v>
       </c>
-      <c r="J11" s="0"/>
       <c r="K11" s="1" t="s">
         <v>28</v>
       </c>
@@ -795,7 +808,6 @@
       <c r="I12" s="1" t="n">
         <v>0.53</v>
       </c>
-      <c r="J12" s="0"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
@@ -825,7 +837,6 @@
       <c r="I13" s="1" t="n">
         <v>0.54</v>
       </c>
-      <c r="J13" s="0"/>
       <c r="K13" s="1" t="s">
         <v>30</v>
       </c>
@@ -858,7 +869,6 @@
       <c r="I14" s="1" t="n">
         <v>0.67</v>
       </c>
-      <c r="J14" s="0"/>
       <c r="K14" s="1" t="s">
         <v>33</v>
       </c>
@@ -891,7 +901,6 @@
       <c r="I15" s="1" t="n">
         <v>0.68</v>
       </c>
-      <c r="J15" s="0"/>
       <c r="K15" s="1" t="s">
         <v>34</v>
       </c>
@@ -924,14 +933,10 @@
       <c r="I16" s="1" t="n">
         <v>0.78</v>
       </c>
-      <c r="J16" s="0"/>
       <c r="K16" s="1" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J17" s="0"/>
-    </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
         <v>11</v>
@@ -960,7 +965,6 @@
       <c r="I18" s="1" t="n">
         <v>0.7</v>
       </c>
-      <c r="J18" s="0"/>
       <c r="K18" s="1" t="s">
         <v>16</v>
       </c>
@@ -993,7 +997,6 @@
       <c r="I19" s="1" t="n">
         <v>0.7</v>
       </c>
-      <c r="J19" s="0"/>
       <c r="K19" s="1" t="s">
         <v>40</v>
       </c>
@@ -1026,7 +1029,6 @@
       <c r="I20" s="1" t="n">
         <v>0.69</v>
       </c>
-      <c r="J20" s="0"/>
       <c r="K20" s="1" t="s">
         <v>41</v>
       </c>
@@ -1059,7 +1061,6 @@
       <c r="I21" s="1" t="n">
         <v>0.69</v>
       </c>
-      <c r="J21" s="0"/>
       <c r="K21" s="1" t="s">
         <v>41</v>
       </c>
@@ -1092,7 +1093,6 @@
       <c r="I22" s="1" t="n">
         <v>0.69</v>
       </c>
-      <c r="J22" s="0"/>
       <c r="K22" s="1" t="s">
         <v>41</v>
       </c>
@@ -1125,7 +1125,6 @@
       <c r="I23" s="1" t="n">
         <v>0.69</v>
       </c>
-      <c r="J23" s="0"/>
       <c r="K23" s="1" t="s">
         <v>41</v>
       </c>
@@ -1158,7 +1157,6 @@
       <c r="I24" s="1" t="n">
         <v>0.71</v>
       </c>
-      <c r="J24" s="0"/>
       <c r="K24" s="1" t="s">
         <v>41</v>
       </c>
@@ -1191,7 +1189,6 @@
       <c r="I25" s="1" t="n">
         <v>0.7</v>
       </c>
-      <c r="J25" s="0"/>
       <c r="K25" s="1" t="s">
         <v>41</v>
       </c>
@@ -1224,7 +1221,6 @@
       <c r="I26" s="1" t="n">
         <v>0.71</v>
       </c>
-      <c r="J26" s="0"/>
       <c r="K26" s="1" t="s">
         <v>43</v>
       </c>
@@ -1257,7 +1253,6 @@
       <c r="I27" s="1" t="n">
         <v>0.72</v>
       </c>
-      <c r="J27" s="0"/>
       <c r="K27" s="1" t="s">
         <v>43</v>
       </c>
@@ -1290,7 +1285,6 @@
       <c r="I28" s="1" t="n">
         <v>0.68</v>
       </c>
-      <c r="J28" s="0"/>
       <c r="K28" s="1" t="s">
         <v>45</v>
       </c>
@@ -1323,7 +1317,6 @@
       <c r="I29" s="1" t="n">
         <v>0.68</v>
       </c>
-      <c r="J29" s="0"/>
       <c r="K29" s="1" t="s">
         <v>45</v>
       </c>
@@ -1356,9 +1349,66 @@
       <c r="I30" s="1" t="n">
         <v>0.83</v>
       </c>
-      <c r="J30" s="0"/>
       <c r="K30" s="1" t="s">
         <v>48</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B32" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="C32" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="D32" s="0" t="s">
+        <v>50</v>
+      </c>
+      <c r="E32" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="F32" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="G32" s="0" t="s">
+        <v>52</v>
+      </c>
+      <c r="H32" s="3" t="n">
+        <v>0.8972</v>
+      </c>
+      <c r="I32" s="0" t="n">
+        <v>0.883</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B33" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="C33" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="D33" s="0" t="s">
+        <v>50</v>
+      </c>
+      <c r="E33" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="F33" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="G33" s="0" t="s">
+        <v>52</v>
+      </c>
+      <c r="H33" s="3" t="n">
+        <v>0.9723</v>
+      </c>
+      <c r="I33" s="0" t="n">
+        <v>0.97</v>
       </c>
     </row>
   </sheetData>
